--- a/backend/excelfiles/ECATScoresTemplate.xlsx
+++ b/backend/excelfiles/ECATScoresTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mark\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0535F157-BC4E-44FF-A8BD-51AC74DBFBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50D3BB8-BAF7-43D5-9A1A-35FCDFECE4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3416FEF9-32DB-4731-A74A-5791F5F26A4C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3416FEF9-32DB-4731-A74A-5791F5F26A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Entrance_Exam" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Applicant ID</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Program</t>
-  </si>
-  <si>
     <t>English</t>
   </si>
   <si>
@@ -52,21 +46,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Monacillo, Princess Mica</t>
-  </si>
-  <si>
-    <t>BSINFOTECH</t>
-  </si>
-  <si>
-    <t>Supnet, April Preceous</t>
-  </si>
-  <si>
-    <t>Echague, Kate Mahusay</t>
-  </si>
-  <si>
-    <t>Ebojo, Darein Echague V</t>
   </si>
   <si>
     <t>PASSED</t>
@@ -137,9 +116,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +156,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +262,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +404,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -433,17 +412,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BFEFB9-C572-43C0-9B0F-6A383F1A43AF}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="43.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
-    <col min="4" max="8" width="11.21875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.1796875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,36 +433,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>2025100029</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
+        <v>2026100002</v>
+      </c>
+      <c r="B2" s="2">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2">
+        <v>90</v>
       </c>
       <c r="D2" s="2">
         <v>90</v>
@@ -489,104 +466,52 @@
         <v>90</v>
       </c>
       <c r="F2" s="2">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2">
-        <v>90</v>
-      </c>
-      <c r="H2" s="2">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>2025100030</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>90</v>
-      </c>
-      <c r="E3" s="2">
-        <v>90</v>
-      </c>
-      <c r="F3" s="2">
-        <v>90</v>
-      </c>
-      <c r="G3" s="2">
-        <v>90</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
+        <v>2026100003</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2025100031</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2">
-        <v>90</v>
-      </c>
-      <c r="F4" s="2">
-        <v>90</v>
-      </c>
-      <c r="G4" s="2">
-        <v>90</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2025100032</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2">
-        <v>90</v>
-      </c>
-      <c r="E5" s="2">
-        <v>90</v>
-      </c>
-      <c r="F5" s="2">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2">
-        <v>90</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
